--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="165">
   <si>
     <t/>
   </si>
@@ -121,6 +121,18 @@
     <t>MAMY/P PNT STD XXL18</t>
   </si>
   <si>
+    <t>20095875</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 28'S L</t>
+  </si>
+  <si>
+    <t>20095874</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 30'S M</t>
+  </si>
+  <si>
     <t>20045421</t>
   </si>
   <si>
@@ -133,82 +145,94 @@
     <t>MAMY POKO 44'S NB</t>
   </si>
   <si>
+    <t>20045423</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL26</t>
+  </si>
+  <si>
+    <t>20045418</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD S38</t>
+  </si>
+  <si>
+    <t>20045419</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M32</t>
+  </si>
+  <si>
+    <t>20045422</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L28</t>
+  </si>
+  <si>
+    <t>20064973</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M48</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20064972</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L42</t>
+  </si>
+  <si>
+    <t>20125288</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL38</t>
+  </si>
+  <si>
+    <t>20141251</t>
+  </si>
+  <si>
+    <t>M.POKO PANT XXXL 22S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20095876</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 23S XL</t>
+  </si>
+  <si>
     <t>20041257</t>
   </si>
   <si>
     <t>MAMY/P DIAPERS S-24S</t>
   </si>
   <si>
-    <t>20141251</t>
-  </si>
-  <si>
-    <t>M.POKO PANT XXXL 22S</t>
-  </si>
-  <si>
-    <t>20045418</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD S38</t>
-  </si>
-  <si>
-    <t>20045419</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M32</t>
-  </si>
-  <si>
-    <t>20045423</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL26</t>
-  </si>
-  <si>
-    <t>20045422</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L28</t>
-  </si>
-  <si>
-    <t>20064973</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M48</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20064972</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L42</t>
-  </si>
-  <si>
-    <t>20125288</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL38</t>
-  </si>
-  <si>
-    <t>20095876</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 23S XL</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20095874</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 30'S M</t>
-  </si>
-  <si>
-    <t>20095875</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 28'S L</t>
+    <t>20142684</t>
+  </si>
+  <si>
+    <t>INDOMARET DPERS 26XL</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20136706</t>
+  </si>
+  <si>
+    <t>IDM BABY DPRS L28</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136707</t>
+  </si>
+  <si>
+    <t>IDM DPRS PANTS M32</t>
   </si>
   <si>
     <t>20137969</t>
@@ -217,22 +241,7 @@
     <t>IDM UNDERPADS 10'S</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20136707</t>
-  </si>
-  <si>
-    <t>IDM DPRS PANTS M32</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136706</t>
-  </si>
-  <si>
-    <t>IDM BABY DPRS L28</t>
+    <t>9</t>
   </si>
   <si>
     <t>20123072</t>
@@ -241,9 +250,6 @@
     <t>SWEETY BRNZE XXL/20S</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
@@ -256,154 +262,181 @@
     <t>RT</t>
   </si>
   <si>
+    <t>20112586</t>
+  </si>
+  <si>
+    <t>SWTY SLV PANT S 38'S</t>
+  </si>
+  <si>
+    <t>20073639</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE L/28'S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20073640</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE XL/24S</t>
+  </si>
+  <si>
+    <t>20092521</t>
+  </si>
+  <si>
+    <t>SWEETY SLV PANT 28 L</t>
+  </si>
+  <si>
+    <t>20092520</t>
+  </si>
+  <si>
+    <t>SWEETY SLV PANT 32 M</t>
+  </si>
+  <si>
+    <t>20083489</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE S 38'S</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20073638</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE M/32'S</t>
+  </si>
+  <si>
+    <t>20083937</t>
+  </si>
+  <si>
+    <t>SWEETY SLV PANT 24XL</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20126742</t>
+  </si>
+  <si>
+    <t>SWEETY SLVR NB-S 40</t>
+  </si>
+  <si>
+    <t>20113354</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE 44S NB</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
+  </si>
+  <si>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
+  </si>
+  <si>
+    <t>20140872</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT XL-32S</t>
+  </si>
+  <si>
+    <t>20108881</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 32+2S M</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20098000</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 28+2S L</t>
+  </si>
+  <si>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
+  </si>
+  <si>
+    <t>20139956</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 38S NB-S</t>
+  </si>
+  <si>
+    <t>20135747</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAP XL24</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>20132849</t>
+  </si>
+  <si>
+    <t>HAPPY NAPY PANT 24XL</t>
+  </si>
+  <si>
+    <t>20130078</t>
+  </si>
+  <si>
+    <t>BABY HP PNKFONG L-28</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20130077</t>
+  </si>
+  <si>
+    <t>BABY HP PNKFONG M-32</t>
+  </si>
+  <si>
     <t>20097386</t>
   </si>
   <si>
     <t>HAPPY NAPPY PANT 28L</t>
   </si>
   <si>
-    <t>20132849</t>
-  </si>
-  <si>
-    <t>HAPPY NAPY PANT 24XL</t>
-  </si>
-  <si>
-    <t>20073639</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE L/28'S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20073640</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE XL/24S</t>
-  </si>
-  <si>
-    <t>20092520</t>
-  </si>
-  <si>
-    <t>SWEETY SLV PANT 32 M</t>
-  </si>
-  <si>
-    <t>20083937</t>
-  </si>
-  <si>
-    <t>SWEETY SLV PANT 24XL</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
     <t>20097385</t>
   </si>
   <si>
     <t>HAPPY NAPPY PANT 32M</t>
   </si>
   <si>
-    <t>20083489</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE S 38'S</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20073638</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE M/32'S</t>
-  </si>
-  <si>
-    <t>20126742</t>
-  </si>
-  <si>
-    <t>SWEETY SLVR NB-S 40</t>
-  </si>
-  <si>
-    <t>20112586</t>
-  </si>
-  <si>
-    <t>SWTY SLV PANT S 38'S</t>
-  </si>
-  <si>
-    <t>20092521</t>
-  </si>
-  <si>
-    <t>SWEETY SLV PANT 28 L</t>
-  </si>
-  <si>
-    <t>20113354</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE 44S NB</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
-  </si>
-  <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
-  </si>
-  <si>
-    <t>20140872</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT XL-32S</t>
-  </si>
-  <si>
-    <t>20108881</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 32+2S M</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20098000</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 28+2S L</t>
-  </si>
-  <si>
-    <t>20139956</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 38S NB-S</t>
-  </si>
-  <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
-  </si>
-  <si>
-    <t>20130078</t>
-  </si>
-  <si>
-    <t>BABY HP PNKFONG L-28</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20130077</t>
-  </si>
-  <si>
-    <t>BABY HP PNKFONG M-32</t>
+    <t>20070712</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS28 L</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>20077483</t>
@@ -412,69 +445,42 @@
     <t>MERRIES PANT GS26 XL</t>
   </si>
   <si>
+    <t>20112938</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS18XXL</t>
+  </si>
+  <si>
+    <t>20072919</t>
+  </si>
+  <si>
+    <t>BABY HAPY PANTS L 20</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20134306</t>
+  </si>
+  <si>
+    <t>BABY HP PNTS 24S XXL</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20103165</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS40 S</t>
+  </si>
+  <si>
     <t>20070711</t>
   </si>
   <si>
     <t>MERRIES PANT GS32 M</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20103165</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS40 S</t>
-  </si>
-  <si>
-    <t>20112938</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS18XXL</t>
-  </si>
-  <si>
-    <t>20070712</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS28 L</t>
-  </si>
-  <si>
-    <t>20135747</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAP XL24</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>20072919</t>
-  </si>
-  <si>
-    <t>BABY HAPY PANTS L 20</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20134306</t>
-  </si>
-  <si>
-    <t>BABY HP PNTS 24S XXL</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
     <t>20134007</t>
   </si>
   <si>
@@ -484,16 +490,16 @@
     <t>18</t>
   </si>
   <si>
+    <t>20072924</t>
+  </si>
+  <si>
+    <t>BABY HAPY PANTS26/XL</t>
+  </si>
+  <si>
     <t>20072925</t>
   </si>
   <si>
     <t>BABY HAPY PANTS 28/L</t>
-  </si>
-  <si>
-    <t>20072924</t>
-  </si>
-  <si>
-    <t>BABY HAPY PANTS26/XL</t>
   </si>
   <si>
     <t>20072923</t>
@@ -892,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1200,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1240,7 +1246,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1320,7 +1326,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1480,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1540,15 +1546,15 @@
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1560,15 +1566,15 @@
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1580,7 +1586,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1600,7 +1606,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1640,7 +1646,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1660,7 +1666,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1680,27 +1686,27 @@
         <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1714,33 +1720,33 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1754,13 +1760,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1774,53 +1780,53 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1834,13 +1840,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1854,53 +1860,53 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1914,13 +1920,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1934,50 +1940,50 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="E53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>71</v>
@@ -1985,19 +1991,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>71</v>
@@ -2005,122 +2011,122 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2134,53 +2140,53 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,30 +2200,30 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>71</v>
@@ -2234,10 +2240,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>71</v>
@@ -2254,12 +2260,32 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>71</v>
       </c>
     </row>

--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -100,7 +100,7 @@
     <t>20021393</t>
   </si>
   <si>
-    <t>MAMY/P PANT STD XL20</t>
+    <t>MAMY/P PANT STD XL</t>
   </si>
   <si>
     <t>20021392</t>

--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -100,7 +100,7 @@
     <t>20021393</t>
   </si>
   <si>
-    <t>MAMY/P PANT STD XL</t>
+    <t>MAMY/P PANT STD XL20</t>
   </si>
   <si>
     <t>20021392</t>

--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -11,215 +11,191 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="155">
   <si>
     <t/>
   </si>
   <si>
-    <t>20136043</t>
-  </si>
-  <si>
-    <t>FITTI PNTS 40S/SMALL</t>
+    <t>20024306</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT BOY XL24</t>
   </si>
   <si>
     <t>DIA03S</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20024303</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT BOY L28</t>
+  </si>
+  <si>
+    <t>20121396</t>
+  </si>
+  <si>
+    <t>MAMY POKO SC M32+2'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20121399</t>
+  </si>
+  <si>
+    <t>MAMY POKO SC L 28'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20021393</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL20</t>
+  </si>
+  <si>
+    <t>20021392</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L20</t>
+  </si>
+  <si>
+    <t>20021391</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M20</t>
+  </si>
+  <si>
+    <t>20021394</t>
+  </si>
+  <si>
+    <t>MAMY/P PNT STD XXL18</t>
+  </si>
+  <si>
+    <t>20095875</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 28'S L</t>
+  </si>
+  <si>
+    <t>20095874</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 30'S M</t>
+  </si>
+  <si>
+    <t>20045421</t>
+  </si>
+  <si>
+    <t>MAMY/P PNT/STD XXL24</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20106150</t>
+  </si>
+  <si>
+    <t>MAMY POKO 44'S NB</t>
+  </si>
+  <si>
+    <t>20045423</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL26</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20045418</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD S38</t>
+  </si>
+  <si>
+    <t>20045419</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M32</t>
+  </si>
+  <si>
+    <t>20045422</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L28</t>
+  </si>
+  <si>
+    <t>20064973</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M48</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20064972</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L42</t>
+  </si>
+  <si>
+    <t>20125288</t>
+  </si>
+  <si>
+    <t>MAMY/P PANT STD XL38</t>
+  </si>
+  <si>
+    <t>20141251</t>
+  </si>
+  <si>
+    <t>M.POKO PANT XXXL 22S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20095876</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 23S XL</t>
+  </si>
+  <si>
+    <t>20041257</t>
+  </si>
+  <si>
+    <t>MAMY/P DIAPERS S-24S</t>
+  </si>
+  <si>
+    <t>20137969</t>
+  </si>
+  <si>
+    <t>IDM UNDERPADS 10'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20142684</t>
+  </si>
+  <si>
+    <t>INDOMARET DPERS 26XL</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20104405</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 32-M</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20104406</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 28-L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20104407</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 26-XL</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20132816</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 24'S XXL</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20024306</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT BOY XL24</t>
-  </si>
-  <si>
-    <t>20024303</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT BOY L28</t>
-  </si>
-  <si>
-    <t>20121396</t>
-  </si>
-  <si>
-    <t>MAMY POKO SC M32+2'S</t>
-  </si>
-  <si>
-    <t>20121399</t>
-  </si>
-  <si>
-    <t>MAMY POKO SC L 28'S</t>
-  </si>
-  <si>
-    <t>20021393</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL20</t>
-  </si>
-  <si>
-    <t>20021392</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L20</t>
-  </si>
-  <si>
-    <t>20021391</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M20</t>
-  </si>
-  <si>
-    <t>20021394</t>
-  </si>
-  <si>
-    <t>MAMY/P PNT STD XXL18</t>
-  </si>
-  <si>
-    <t>20095875</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 28'S L</t>
-  </si>
-  <si>
-    <t>20095874</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 30'S M</t>
-  </si>
-  <si>
-    <t>20045421</t>
-  </si>
-  <si>
-    <t>MAMY/P PNT/STD XXL24</t>
-  </si>
-  <si>
-    <t>20106150</t>
-  </si>
-  <si>
-    <t>MAMY POKO 44'S NB</t>
-  </si>
-  <si>
-    <t>20045423</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL26</t>
-  </si>
-  <si>
-    <t>20045418</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD S38</t>
-  </si>
-  <si>
-    <t>20045419</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M32</t>
-  </si>
-  <si>
-    <t>20045422</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L28</t>
-  </si>
-  <si>
-    <t>20064973</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M48</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20064972</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L42</t>
-  </si>
-  <si>
-    <t>20125288</t>
-  </si>
-  <si>
-    <t>MAMY/P PANT STD XL38</t>
-  </si>
-  <si>
-    <t>20141251</t>
-  </si>
-  <si>
-    <t>M.POKO PANT XXXL 22S</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20095876</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 23S XL</t>
-  </si>
-  <si>
-    <t>20041257</t>
-  </si>
-  <si>
-    <t>MAMY/P DIAPERS S-24S</t>
-  </si>
-  <si>
-    <t>20142684</t>
-  </si>
-  <si>
-    <t>INDOMARET DPERS 26XL</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>20136706</t>
   </si>
   <si>
@@ -235,19 +211,13 @@
     <t>IDM DPRS PANTS M32</t>
   </si>
   <si>
-    <t>20137969</t>
-  </si>
-  <si>
-    <t>IDM UNDERPADS 10'S</t>
+    <t>20123072</t>
+  </si>
+  <si>
+    <t>SWEETY BRNZE XXL/20S</t>
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20123072</t>
-  </si>
-  <si>
-    <t>SWEETY BRNZE XXL/20S</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
@@ -898,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -943,18 +913,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -963,18 +933,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -983,18 +953,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1003,270 +973,270 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,13 +1250,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1300,13 +1270,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1320,53 +1290,53 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1380,101 +1350,101 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1486,15 +1456,15 @@
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1503,198 +1473,198 @@
         <v>68</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1706,15 +1676,15 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1723,18 +1693,18 @@
         <v>96</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1743,398 +1713,398 @@
         <v>96</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2146,15 +2116,15 @@
         <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2163,18 +2133,18 @@
         <v>148</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2183,110 +2153,10 @@
         <v>148</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
